--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20232.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -82,34 +82,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
@@ -118,22 +118,22 @@
     <t>NIEVES</t>
   </si>
   <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>ESPINDOLA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
+    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>YAHIR</t>
@@ -142,31 +142,25 @@
     <t>CANDIDO</t>
   </si>
   <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
     <t>JORGE MARIO</t>
   </si>
   <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
+    <t>NAHOMY</t>
   </si>
 </sst>
 </file>
@@ -762,16 +756,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -785,16 +782,19 @@
         <v>37</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>37</v>
       </c>
-      <c r="E3">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -808,16 +808,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -831,16 +834,19 @@
         <v>31</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>31</v>
       </c>
-      <c r="E5">
-        <v>31</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -854,16 +860,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H6">
+        <v>6.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -877,16 +886,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>86.48999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -942,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>76.67</v>
+        <v>70</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -977,7 +989,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -994,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1020,16 +1032,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1046,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>67.86</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1081,7 +1093,7 @@
         <v>86.48999999999999</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,16 +1135,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920171</v>
+        <v>21330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,16 +1158,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920176</v>
+        <v>21330051920171</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,22 +1181,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920334</v>
+        <v>21330051920176</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1192,16 +1204,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920207</v>
+        <v>21330051920209</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1215,22 +1227,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920209</v>
+        <v>21330051920307</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1238,7 +1250,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920289</v>
+        <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1247,7 +1259,7 @@
         <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1261,7 +1273,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920337</v>
+        <v>21330051920330</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1270,7 +1282,7 @@
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1284,45 +1296,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920323</v>
+        <v>21330051920001</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920001</v>
+        <v>21330051920289</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1330,47 +1342,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920166</v>
+        <v>19330051920208</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920250</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20232.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,85 +82,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
   </si>
 </sst>
 </file>
@@ -636,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -645,10 +624,10 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>96.77</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
         <v>8.5</v>
@@ -831,7 +810,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -840,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -954,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -989,7 +968,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1006,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1026,7 +1005,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1035,13 +1014,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1058,16 +1037,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1084,16 +1063,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>86.48999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,16 +1114,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>21330051920164</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,16 +1137,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1181,22 +1160,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920176</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1204,16 +1183,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920209</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1227,22 +1206,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920307</v>
+        <v>21330051920213</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1250,16 +1229,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920323</v>
+        <v>19330051920208</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1268,21 +1247,21 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920330</v>
+        <v>21330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1291,75 +1270,6 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920001</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920289</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920208</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>
